--- a/output/xlsx/OperadorDeEcommerceRegistraOcorrenciaEmNotaDePicking--GT-.xlsx
+++ b/output/xlsx/OperadorDeEcommerceRegistraOcorrenciaEmNotaDePicking--GT-.xlsx
@@ -107,7 +107,7 @@
     <t>SYSTEM mostra tela com dados de Picking</t>
   </si>
   <si>
-    <t>Operador: clica no botao 'Registrar Ocorrencia' para uma determinada nota</t>
+    <t>Operador: clica no botao 'Registrar Ocorrencia'</t>
   </si>
   <si>
     <t>SYSTEM abre a janela de registro da Ocorrencia</t>
@@ -155,13 +155,13 @@
     <t>SYSTEM processes action successfully</t>
   </si>
   <si>
-    <t>Operador: nao insere a descricao da ocorrencia e clica no botao de 'Registrar'</t>
+    <t>Operador: nao insere a descricao da ocorrencia e clica no botao de 'Salvar'</t>
   </si>
   <si>
     <t>SYSTEM informa que a mensagem da ocorrencia nao pode ser vazia</t>
   </si>
   <si>
-    <t>Operador: insere descricao valida para Ocorrencia e clica no botao 'Registrar'</t>
+    <t>Operador: insere descricao valida para Ocorrencia e clica no botao 'Salvar'</t>
   </si>
   <si>
     <t>Flow interrupted due to exception / error</t>
